--- a/vse-loti/341395410/spec-341395410.xlsx
+++ b/vse-loti/341395410/spec-341395410.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -94,6 +94,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -462,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -599,19 +602,36 @@
         <v>2023980.45</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22% (справочно):</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>2469256.15</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; закупка по 223-ФЗ, включать налоги в цену закон не требует — суммы взяты как в документе («без НДС»). «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
           <t>Источник: 1 Извещение 3434.docx
 3 Приложение №1 техническое задание 3434.docx</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:B9"/>
+    <mergeCell ref="A9:B11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341395410/spec-341395410.xlsx
+++ b/vse-loti/341395410/spec-341395410.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -477,6 +477,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -512,17 +513,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -551,7 +557,7 @@
       <c r="F2" s="4" t="n">
         <v>12.272</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -579,7 +585,7 @@
       <c r="F3" s="4" t="n">
         <v>11.956</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -598,7 +604,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="H5" s="7" t="n">
         <v>2023980.45</v>
       </c>
     </row>
@@ -608,7 +614,7 @@
           <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="J6" s="7" t="n">
         <v>2469256.15</v>
       </c>
     </row>
